--- a/Design/Excel/ET/Datas/Product/SupplyConfig.xlsx
+++ b/Design/Excel/ET/Datas/Product/SupplyConfig.xlsx
@@ -1128,7 +1128,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr/>
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:J8"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="6"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -1188,6 +1188,11 @@
           <t>ReceivingLayoutId</t>
         </is>
       </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>MenuVariant</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1235,6 +1240,11 @@
           <t>int</t>
         </is>
       </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1282,6 +1292,11 @@
           <t>ReceivingLayoutId</t>
         </is>
       </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>MenuVariant</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1315,6 +1330,11 @@
       <c r="I4" s="0">
         <v>4</v>
       </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1348,6 +1368,11 @@
       <c r="I5" s="0">
         <v>4</v>
       </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1380,6 +1405,99 @@
       </c>
       <c r="I6" s="0">
         <v>4</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>橙子补货</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="F7">
+        <v>2</v>
+      </c>
+      <c r="G7">
+        <v>5</v>
+      </c>
+      <c r="H7">
+        <v>40</v>
+      </c>
+      <c r="I7" s="0">
+        <v>4</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>空杯补货</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="F8">
+        <v>2</v>
+      </c>
+      <c r="G8">
+        <v>5</v>
+      </c>
+      <c r="H8">
+        <v>40</v>
+      </c>
+      <c r="I8" s="0">
+        <v>4</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/Design/Excel/ET/Datas/Product/SupplyConfig.xlsx
+++ b/Design/Excel/ET/Datas/Product/SupplyConfig.xlsx
@@ -939,679 +939,699 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
-  <x:cols>
-    <x:col min="1" max="1" width="21.125" style="2" customWidth="1"/>
-    <x:col min="2" max="2" width="12.75" style="2" customWidth="1"/>
-    <x:col min="3" max="4" width="12.625" style="2" customWidth="1"/>
-    <x:col min="5" max="5" width="15.125" style="2" customWidth="1"/>
-    <x:col min="6" max="6" width="9.625" style="2" customWidth="1"/>
-    <x:col min="7" max="7" width="28.75" style="2" customWidth="1"/>
-    <x:col min="8" max="9" width="11.75" style="2" customWidth="1"/>
-    <x:col min="10" max="10" width="6.75" style="2" customWidth="1"/>
-    <x:col min="11" max="16384" width="9" style="2" customWidth="0"/>
-  </x:cols>
-  <x:sheetData>
-    <x:row r="1">
-      <x:c r="A1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">##var</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Id</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Name</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">MaterialDefinitionId</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">PackageDefinitionId</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">PackageUnits</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">AvailablePackages</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">TransitTicks</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ReceivingLayoutId</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="J1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">MenuVariant</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="2">
-      <x:c r="A2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">##type</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">int</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">string</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">int</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">int</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">int</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">int</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">int</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">int</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="J2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">int</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="3">
-      <x:c r="A3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">##</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Id</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Name</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">MaterialDefinitionId</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">PackageDefinitionId</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">PackageUnits</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">AvailablePackages</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">TransitTicks</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ReceivingLayoutId</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="J3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">MenuVariant</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="4">
-      <x:c r="A4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve"/>
-        </x:is>
-      </x:c>
-      <x:c r="B4">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">番茄补货</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D4">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E4">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="F4">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="G4">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="H4">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="I4">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="J4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">0</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="5">
-      <x:c r="A5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve"/>
-        </x:is>
-      </x:c>
-      <x:c r="B5">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">鸡蛋补货</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D5">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E5">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="F5">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="G5">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="H5">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="I5">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="J5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">0</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="6">
-      <x:c r="A6" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve"/>
-        </x:is>
-      </x:c>
-      <x:c r="B6">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C6" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">面包补货</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D6">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="E6">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F6">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="G6">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="H6">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="I6">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="J6" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">0</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="7">
-      <x:c r="A7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve"/>
-        </x:is>
-      </x:c>
-      <x:c r="B7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">4</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">橙子补货</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">15</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">20</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F7">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="G7">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="H7">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="I7">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="J7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">1</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="8">
-      <x:c r="A8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve"/>
-        </x:is>
-      </x:c>
-      <x:c r="B8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">5</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">空杯补货</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">19</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">21</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F8">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="G8">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="H8">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="I8">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="J8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">1</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="9">
-      <x:c r="A9" t="str"/>
-      <x:c r="B9" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C9" t="str">
-        <x:v>生菜补货</x:v>
-      </x:c>
-      <x:c r="D9" t="n">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="E9" t="n">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="F9" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="G9" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="H9" t="n">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="I9" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="J9" t="n">
-        <x:v>2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10">
-      <x:c r="A10" t="str"/>
-      <x:c r="B10" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C10" t="str">
-        <x:v>黄瓜补货</x:v>
-      </x:c>
-      <x:c r="D10" t="n">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="E10" t="n">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="F10" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="G10" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="H10" t="n">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="I10" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="J10" t="n">
-        <x:v>2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11">
-      <x:c r="A11" t="str"/>
-      <x:c r="B11" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C11" t="str">
-        <x:v>芝士补货</x:v>
-      </x:c>
-      <x:c r="D11" t="n">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="E11" t="n">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="F11" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="G11" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="H11" t="n">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="I11" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="J11" t="n">
-        <x:v>2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12">
-      <x:c r="A12" t="str"/>
-      <x:c r="B12" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C12" t="str">
-        <x:v>汉堡面包补货</x:v>
-      </x:c>
-      <x:c r="D12" t="n">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="E12" t="n">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="F12" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G12" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="H12" t="n">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="I12" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="J12" t="n">
-        <x:v>4</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13">
-      <x:c r="A13" t="str"/>
-      <x:c r="B13" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C13" t="str">
-        <x:v>牛肉饼补货</x:v>
-      </x:c>
-      <x:c r="D13" t="n">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="E13" t="n">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="F13" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G13" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="H13" t="n">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="I13" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="J13" t="n">
-        <x:v>4</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14">
-      <x:c r="A14" t="str"/>
-      <x:c r="B14" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="C14" t="str">
-        <x:v>香肠补货</x:v>
-      </x:c>
-      <x:c r="D14" t="n">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="E14" t="n">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="F14" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G14" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="H14" t="n">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="I14" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="J14" t="n">
-        <x:v>4</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15">
-      <x:c r="A15" t="str"/>
-      <x:c r="B15" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="C15" t="str">
-        <x:v>预拌粉补货</x:v>
-      </x:c>
-      <x:c r="D15" t="n">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="E15" t="n">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="F15" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G15" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="H15" t="n">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="I15" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="J15" t="n">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16">
-      <x:c r="A16" t="str"/>
-      <x:c r="B16" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C16" t="str">
-        <x:v>牛奶补货</x:v>
-      </x:c>
-      <x:c r="D16" t="n">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="E16" t="n">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="F16" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G16" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="H16" t="n">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="I16" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="J16" t="n">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17">
-      <x:c r="A17" t="str"/>
-      <x:c r="B17" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C17" t="str">
-        <x:v>咖啡豆补货</x:v>
-      </x:c>
-      <x:c r="D17" t="n">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="E17" t="n">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="F17" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G17" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="H17" t="n">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="I17" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="J17" t="n">
-        <x:v>6</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18">
-      <x:c r="A18" t="str"/>
-      <x:c r="B18" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C18" t="str">
-        <x:v>热饮杯补货</x:v>
-      </x:c>
-      <x:c r="D18" t="n">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="E18" t="n">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="F18" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="G18" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="H18" t="n">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="I18" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="J18" t="n">
-        <x:v>6</x:v>
-      </x:c>
-    </x:row>
-  </x:sheetData>
-  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</x:worksheet>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
+  <cols>
+    <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
+    <col min="2" max="2" width="12.75" style="2" customWidth="1"/>
+    <col min="3" max="4" width="12.625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="15.125" style="2" customWidth="1"/>
+    <col min="6" max="6" width="9.625" style="2" customWidth="1"/>
+    <col min="7" max="7" width="28.75" style="2" customWidth="1"/>
+    <col min="8" max="9" width="11.75" style="2" customWidth="1"/>
+    <col min="10" max="10" width="6.75" style="2" customWidth="1"/>
+    <col min="11" max="16384" width="9" style="2" customWidth="0"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">##var</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Id</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Name</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MaterialDefinitionId</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PackageDefinitionId</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PackageUnits</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AvailablePackages</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TransitTicks</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ReceivingLayoutId</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MenuVariant</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">##type</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">int</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">string</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">int</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">int</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">int</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">int</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">int</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">int</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>ProductMenuVariant</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">##</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Id</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Name</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MaterialDefinitionId</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PackageDefinitionId</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PackageUnits</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AvailablePackages</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TransitTicks</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ReceivingLayoutId</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MenuVariant</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">番茄补货</t>
+        </is>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="E4">
+        <v>12</v>
+      </c>
+      <c r="F4">
+        <v>2</v>
+      </c>
+      <c r="G4">
+        <v>5</v>
+      </c>
+      <c r="H4">
+        <v>40</v>
+      </c>
+      <c r="I4">
+        <v>4</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="B5">
+        <v>2</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">鸡蛋补货</t>
+        </is>
+      </c>
+      <c r="D5">
+        <v>3</v>
+      </c>
+      <c r="E5">
+        <v>13</v>
+      </c>
+      <c r="F5">
+        <v>2</v>
+      </c>
+      <c r="G5">
+        <v>5</v>
+      </c>
+      <c r="H5">
+        <v>40</v>
+      </c>
+      <c r="I5">
+        <v>4</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="B6">
+        <v>3</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">面包补货</t>
+        </is>
+      </c>
+      <c r="D6">
+        <v>8</v>
+      </c>
+      <c r="E6">
+        <v>14</v>
+      </c>
+      <c r="F6">
+        <v>2</v>
+      </c>
+      <c r="G6">
+        <v>5</v>
+      </c>
+      <c r="H6">
+        <v>40</v>
+      </c>
+      <c r="I6">
+        <v>4</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">橙子补货</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20</t>
+        </is>
+      </c>
+      <c r="F7">
+        <v>2</v>
+      </c>
+      <c r="G7">
+        <v>5</v>
+      </c>
+      <c r="H7">
+        <v>40</v>
+      </c>
+      <c r="I7">
+        <v>4</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Drink</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">空杯补货</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21</t>
+        </is>
+      </c>
+      <c r="F8">
+        <v>2</v>
+      </c>
+      <c r="G8">
+        <v>5</v>
+      </c>
+      <c r="H8">
+        <v>40</v>
+      </c>
+      <c r="I8">
+        <v>4</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Drink</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str"/>
+      <c r="B9" t="n">
+        <v>6</v>
+      </c>
+      <c r="C9" t="str">
+        <v>生菜补货</v>
+      </c>
+      <c r="D9" t="n">
+        <v>22</v>
+      </c>
+      <c r="E9" t="n">
+        <v>29</v>
+      </c>
+      <c r="F9" t="n">
+        <v>2</v>
+      </c>
+      <c r="G9" t="n">
+        <v>5</v>
+      </c>
+      <c r="H9" t="n">
+        <v>40</v>
+      </c>
+      <c r="I9" t="n">
+        <v>4</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Salad</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str"/>
+      <c r="B10" t="n">
+        <v>7</v>
+      </c>
+      <c r="C10" t="str">
+        <v>黄瓜补货</v>
+      </c>
+      <c r="D10" t="n">
+        <v>24</v>
+      </c>
+      <c r="E10" t="n">
+        <v>30</v>
+      </c>
+      <c r="F10" t="n">
+        <v>2</v>
+      </c>
+      <c r="G10" t="n">
+        <v>5</v>
+      </c>
+      <c r="H10" t="n">
+        <v>40</v>
+      </c>
+      <c r="I10" t="n">
+        <v>4</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Salad</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str"/>
+      <c r="B11" t="n">
+        <v>8</v>
+      </c>
+      <c r="C11" t="str">
+        <v>芝士补货</v>
+      </c>
+      <c r="D11" t="n">
+        <v>26</v>
+      </c>
+      <c r="E11" t="n">
+        <v>31</v>
+      </c>
+      <c r="F11" t="n">
+        <v>2</v>
+      </c>
+      <c r="G11" t="n">
+        <v>5</v>
+      </c>
+      <c r="H11" t="n">
+        <v>40</v>
+      </c>
+      <c r="I11" t="n">
+        <v>4</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Salad</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str"/>
+      <c r="B12" t="n">
+        <v>9</v>
+      </c>
+      <c r="C12" t="str">
+        <v>汉堡面包补货</v>
+      </c>
+      <c r="D12" t="n">
+        <v>32</v>
+      </c>
+      <c r="E12" t="n">
+        <v>40</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" t="n">
+        <v>5</v>
+      </c>
+      <c r="H12" t="n">
+        <v>40</v>
+      </c>
+      <c r="I12" t="n">
+        <v>4</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str"/>
+      <c r="B13" t="n">
+        <v>10</v>
+      </c>
+      <c r="C13" t="str">
+        <v>牛肉饼补货</v>
+      </c>
+      <c r="D13" t="n">
+        <v>33</v>
+      </c>
+      <c r="E13" t="n">
+        <v>41</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" t="n">
+        <v>5</v>
+      </c>
+      <c r="H13" t="n">
+        <v>40</v>
+      </c>
+      <c r="I13" t="n">
+        <v>4</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str"/>
+      <c r="B14" t="n">
+        <v>11</v>
+      </c>
+      <c r="C14" t="str">
+        <v>香肠补货</v>
+      </c>
+      <c r="D14" t="n">
+        <v>35</v>
+      </c>
+      <c r="E14" t="n">
+        <v>42</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" t="n">
+        <v>5</v>
+      </c>
+      <c r="H14" t="n">
+        <v>40</v>
+      </c>
+      <c r="I14" t="n">
+        <v>4</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str"/>
+      <c r="B15" t="n">
+        <v>12</v>
+      </c>
+      <c r="C15" t="str">
+        <v>预拌粉补货</v>
+      </c>
+      <c r="D15" t="n">
+        <v>43</v>
+      </c>
+      <c r="E15" t="n">
+        <v>50</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G15" t="n">
+        <v>5</v>
+      </c>
+      <c r="H15" t="n">
+        <v>40</v>
+      </c>
+      <c r="I15" t="n">
+        <v>4</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Dessert</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str"/>
+      <c r="B16" t="n">
+        <v>13</v>
+      </c>
+      <c r="C16" t="str">
+        <v>牛奶补货</v>
+      </c>
+      <c r="D16" t="n">
+        <v>44</v>
+      </c>
+      <c r="E16" t="n">
+        <v>51</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1</v>
+      </c>
+      <c r="G16" t="n">
+        <v>5</v>
+      </c>
+      <c r="H16" t="n">
+        <v>40</v>
+      </c>
+      <c r="I16" t="n">
+        <v>4</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Dessert</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str"/>
+      <c r="B17" t="n">
+        <v>14</v>
+      </c>
+      <c r="C17" t="str">
+        <v>咖啡豆补货</v>
+      </c>
+      <c r="D17" t="n">
+        <v>52</v>
+      </c>
+      <c r="E17" t="n">
+        <v>62</v>
+      </c>
+      <c r="F17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G17" t="n">
+        <v>5</v>
+      </c>
+      <c r="H17" t="n">
+        <v>40</v>
+      </c>
+      <c r="I17" t="n">
+        <v>4</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Cafe</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str"/>
+      <c r="B18" t="n">
+        <v>15</v>
+      </c>
+      <c r="C18" t="str">
+        <v>热饮杯补货</v>
+      </c>
+      <c r="D18" t="n">
+        <v>59</v>
+      </c>
+      <c r="E18" t="n">
+        <v>63</v>
+      </c>
+      <c r="F18" t="n">
+        <v>3</v>
+      </c>
+      <c r="G18" t="n">
+        <v>5</v>
+      </c>
+      <c r="H18" t="n">
+        <v>40</v>
+      </c>
+      <c r="I18" t="n">
+        <v>4</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Cafe</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>